--- a/data/trans_orig/IP07C18-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C18-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13142</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19280</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20636</t>
+          <t>20091</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26533</t>
+          <t>26450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>35646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36677</t>
+          <t>36602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54458</t>
+          <t>54327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70600</t>
+          <t>69977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,26%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33138</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>13809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12958</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>24077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16492</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28018</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9891</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>212</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>30773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>16821</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>33363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>541</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12006</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14435</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24453</t>
+          <t>25387</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>22523</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>15507</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>27581</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>28241</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>43830</t>
+          <t>44159</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27305</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>20500</t>
+          <t>19890</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>31755</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>39829</t>
+          <t>39325</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>56535</t>
+          <t>56467</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>24643</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>38357</t>
+          <t>38652</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>17643</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>29332</t>
+          <t>29615</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>46107</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>63803</t>
+          <t>64516</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>24871</t>
+          <t>24617</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>23876</t>
+          <t>24075</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>37458</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>52225</t>
+          <t>51575</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>71298</t>
+          <t>71402</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18887</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>32581</t>
+          <t>33161</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>107079</t>
+          <t>107153</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>133195</t>
+          <t>133447</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>95034</t>
+          <t>95579</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>122540</t>
+          <t>123528</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>211492</t>
+          <t>211827</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>249283</t>
+          <t>248763</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>101109</t>
+          <t>102148</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>127511</t>
+          <t>127650</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>108062</t>
+          <t>107611</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>135311</t>
+          <t>134636</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>216361</t>
+          <t>215970</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>255334</t>
+          <t>253998</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>54559</t>
+          <t>53354</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>49412</t>
+          <t>48978</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>72002</t>
+          <t>71112</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>117276</t>
+          <t>117433</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>25761</t>
+          <t>24929</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11405</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22678</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27729</t>
+          <t>27979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39145</t>
+          <t>39363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>542</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27858</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38539</t>
+          <t>38505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>30619</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>42240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64015</t>
+          <t>63291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77866</t>
+          <t>78631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9578</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20321</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25308</t>
+          <t>25131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33127</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43501</t>
+          <t>44088</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>16133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,62%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15409</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>24619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>31870</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46516</t>
+          <t>45716</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>63,22%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>14029</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>25555</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16620</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17823</t>
+          <t>17309</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>25767</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>41530</t>
+          <t>41404</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>464</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>37006</t>
+          <t>37126</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>28248</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>39290</t>
+          <t>39619</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>57641</t>
+          <t>57581</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>73530</t>
+          <t>74058</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>37197</t>
+          <t>36685</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11650,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24408</t>
+          <t>24446</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>38478</t>
+          <t>38213</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>15995</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>44122</t>
+          <t>43366</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>62863</t>
+          <t>63073</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>27816</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>41857</t>
+          <t>41415</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>33977</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>48649</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>66494</t>
+          <t>65806</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>86822</t>
+          <t>86859</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>18553</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>15392</t>
+          <t>15530</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>29852</t>
+          <t>28793</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -12337,7 +12337,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>159797</t>
+          <t>160995</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>188713</t>
+          <t>189272</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>153968</t>
+          <t>153186</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>185066</t>
+          <t>183035</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>322703</t>
+          <t>321517</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>364618</t>
+          <t>363346</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>80858</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>107695</t>
+          <t>106827</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>97654</t>
+          <t>99083</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>127103</t>
+          <t>128469</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>186192</t>
+          <t>188936</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>227435</t>
+          <t>227984</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>40423</t>
+          <t>40350</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>38065</t>
+          <t>38003</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>48279</t>
+          <t>48450</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>71579</t>
+          <t>73489</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>21362</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22824</t>
+          <t>22643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19849</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29340</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40715</t>
+          <t>40813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>18117</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29718</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41364</t>
+          <t>41047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27591</t>
+          <t>27182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>39420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>61203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78632</t>
+          <t>77277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>71,49%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16185</t>
+          <t>16529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9994</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18611</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33239</t>
+          <t>33719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>11363</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -14501,12 +14501,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14516,12 +14516,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -14649,12 +14649,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14684,12 +14684,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14544</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23987</t>
+          <t>24098</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33989</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47809</t>
+          <t>47750</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17066</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16199</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29793</t>
+          <t>29593</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -15188,7 +15188,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15223,7 +15223,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15253,12 +15253,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15268,12 +15268,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>17128</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>26163</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19274</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29165</t>
+          <t>28867</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39646</t>
+          <t>39349</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52891</t>
+          <t>53163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13189</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26326</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>14717</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>18725</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31423</t>
+          <t>31249</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14540</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30456</t>
+          <t>30596</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19789</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>34966</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -17116,12 +17116,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17166,12 +17166,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19636</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33391</t>
+          <t>33137</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>28627</t>
+          <t>30049</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>40877</t>
+          <t>40475</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>59022</t>
+          <t>59006</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>34901</t>
+          <t>34389</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33922</t>
+          <t>33721</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>45525</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>65431</t>
+          <t>64733</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>16526</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>14962</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>27864</t>
+          <t>28442</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17911,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17926,12 +17926,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>24233</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>22638</t>
+          <t>23070</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>37447</t>
+          <t>37297</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>50713</t>
+          <t>51264</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>71400</t>
+          <t>70746</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>44626</t>
+          <t>44898</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>26083</t>
+          <t>26520</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>41397</t>
+          <t>40167</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>61077</t>
+          <t>61137</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>80643</t>
+          <t>81434</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,3%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>14884</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>159248</t>
+          <t>158796</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>190111</t>
+          <t>189840</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>146334</t>
+          <t>146506</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>177312</t>
+          <t>178418</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>314395</t>
+          <t>316591</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>361213</t>
+          <t>359336</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>114366</t>
+          <t>114357</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>144579</t>
+          <t>143664</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>117848</t>
+          <t>118900</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>148280</t>
+          <t>147762</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>241557</t>
+          <t>239399</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>283297</t>
+          <t>280912</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>39044</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>53498</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>58115</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>85592</t>
+          <t>85692</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
